--- a/M&A/カンテサンス/カンテサンス_2027年月次CF計画.xlsx
+++ b/M&A/カンテサンス/カンテサンス_2027年月次CF計画.xlsx
@@ -9,8 +9,9 @@
   </bookViews>
   <sheets>
     <sheet name="前提" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="月次CF" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="買収資金" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="月次CF（保守）" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="月次CF（のれん考慮）" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="買収資金" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="137">
   <si>
     <r>
       <rPr>
@@ -260,7 +261,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">万人＋食材原価から逆算</t>
+      <t xml:space="preserve">万人と食材原価から逆算</t>
     </r>
   </si>
   <si>
@@ -695,7 +696,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月は繁忙期のため営業日数を増やす前提。月次売上は営業日数に比例させている。</t>
+      <t xml:space="preserve">月は繁忙期のため営業日数を増減させている。月次売上は営業日数に比例させている。</t>
     </r>
   </si>
   <si>
@@ -847,7 +848,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">の負債に計上されている金額。取得後の会社が納付する</t>
+      <t xml:space="preserve">の負債計上額。譲受価額の算定では控除していないため、取得後の会社が納付する</t>
     </r>
   </si>
   <si>
@@ -950,28 +951,226 @@
       </rPr>
       <t xml:space="preserve">1</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。仮決算による中間申告を行えば圧縮できる</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">（期中の消費税）</t>
   </si>
   <si>
-    <t xml:space="preserve">売上高は税抜表示であり、消費税は預り金の性質を持つ。顧客からの預りと税務署への納付が年間を通じて相殺されるため、本モデルでは計上していない</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">※ 2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
+    <t xml:space="preserve">売上高は税抜表示であり、消費税は預り金の性質を持つ。顧客からの預りと納付が年間で相殺されるため計上していない</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">買収ファイナンス（返済は毎月）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">タームローン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（元金均等・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">毎月返済。月次元本＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷84</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">タームローン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（期限一括）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年後に一括返済。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年間の累積余剰キャッシュフローで返済する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">有利子負債 合計（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -979,8 +1178,264 @@
     </r>
     <r>
       <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝タームローン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。ブリッジローンは合併直後に全額返済済み</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">金利</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">みずほ銀行との協議前提。利息は前月末残高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">金利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で毎月発生</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">月次の元本返済額</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝タームローン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A÷84</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">期首現金（対象会社に留保する運転資金）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">★ 本モデルの主要レバー。ここを増減させると買収時の中野氏の拠出額が同額だけ変動する</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資産調整勘定（税務上ののれん）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">株式譲受代金</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">譲受価額</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億円のケース</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">対象会社の純資産（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -989,344 +1444,145 @@
     </r>
     <r>
       <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月期の未払税金は、譲受価額の算定において控除していない（事業価値の算定は現預金と役員貸付金のみを非事業用資産として扱っている）。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-※ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">合併に伴う資産調整勘定（税務上ののれん）の損金算入は、保守的に織り込んでいない。認められる場合、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年度の法人税はほぼ発生しない。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">買収ファイナンスと期首現金</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">有利子負債（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日、ブリッジ返済後）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">タームローン</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A 14.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億円＋タームローン</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B 6.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億円</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">金利</t>
-  </si>
-  <si>
-    <t xml:space="preserve">みずほ銀行との協議前提</t>
-  </si>
-  <si>
-    <t xml:space="preserve">四半期の元本返済額</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">タームローン</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A 14.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億円を</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年元金均等＝年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億円。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月に返済</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">期首現金（対象会社に留保する運転資金）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">★ 本モデルの主要レバー。ここを増減させると買収時に必要な中野氏の拠出額が同額だけ変動する</t>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月期末・帳簿）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">時価評価によりワイン在庫等の含み益が加算される場合、資産調整勘定はその分減少する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">資産調整勘定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">＝株式譲受代金−時価純資産。非適格合併により計上される税務上ののれん</t>
+  </si>
+  <si>
+    <t xml:space="preserve">償却年数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法人税法上、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月にわたり月割で損金算入される</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">年間の損金算入額</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝資産調整勘定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">償却年数</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">税務上の所得（年間）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">＝営業利益−年間の損金算入額。マイナスであれば法人税は発生しない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 資産調整勘定の計上可否および金額は、合併の適格・非適格の判定と時価純資産の算定によって変動する。デュー・ディリジェンスの税務パートで確認を要する。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 本シートを前提に、シート『月次</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（保守）』は損金算入を織り込まない場合、シート『月次</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（のれん考慮）』は織り込む場合を示している。</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1348,18 +1604,37 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年 月次キャッシュフロー計画（百万円）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">計画どおり（</t>
+      <t xml:space="preserve">年 月次キャッシュフロー計画（百万円）― 保守）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資産調整勘定（税務上ののれん）の損金算入を織り込まない場合。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月に</t>
     </r>
     <r>
       <rPr>
@@ -1397,7 +1672,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月期の会社計画と同水準）に推移した場合。すべて『前提』シートを参照している。</t>
+      <t xml:space="preserve">月期の未払税金、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年度の中間納付が発生する。</t>
     </r>
   </si>
   <si>
@@ -1943,6 +2256,12 @@
     <t xml:space="preserve">営業利益</t>
   </si>
   <si>
+    <t xml:space="preserve">（参考）資産調整勘定の償却　※非資金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（参考）税務上の所得</t>
+  </si>
+  <si>
     <t xml:space="preserve">営業キャッシュフロー</t>
   </si>
   <si>
@@ -1952,7 +2271,7 @@
     <t xml:space="preserve">支払利息</t>
   </si>
   <si>
-    <t xml:space="preserve">借入元本の返済</t>
+    <t xml:space="preserve">借入元本の返済（毎月）</t>
   </si>
   <si>
     <t xml:space="preserve">当月収支</t>
@@ -1964,7 +2283,7 @@
     <t xml:space="preserve">現金 期末残高</t>
   </si>
   <si>
-    <t xml:space="preserve">借入残高（期末）</t>
+    <t xml:space="preserve">有利子負債（期末）</t>
   </si>
   <si>
     <t xml:space="preserve">最低現金残高</t>
@@ -1976,143 +2295,118 @@
     <t xml:space="preserve">年間の営業キャッシュフロー</t>
   </si>
   <si>
+    <t xml:space="preserve">年間の法人税等の納付</t>
+  </si>
+  <si>
     <t xml:space="preserve">年間の元利返済額</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DSCR</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（法人税控除後のキャッシュフローベース）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">※ 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月に</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月期の未払税金、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月に</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年度の中間納付が集中するため、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月末が年間で最も現金残高が薄くなる。</t>
+    <t xml:space="preserve">DSCR</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 借入の返済は毎月。元本は毎月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円（タームローン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A 1,400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷84</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月）、利息は前月末残高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">金利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
     </r>
   </si>
   <si>
@@ -2124,22 +2418,111 @@
         <b val="true"/>
         <sz val="13"/>
         <color rgb="FF6D2E46"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">買収資金の調達と使途（譲受価額</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="13"/>
         <color rgb="FF6D2E46"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50.0</t>
-    </r>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年 月次キャッシュフロー計画（百万円）― のれん考慮）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資産調整勘定の損金算入を織り込む場合。税務上の所得がマイナスとなるため、仮決算による中間申告により</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月の中間納付を回避できる前提。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月の納付は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月期に対応するものであり回避できない。</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -2148,11 +2531,32 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">買収資金の調達と使途（譲受価額</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF6D2E46"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50.0</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF6D2E46"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">億円のケース）</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">『前提』シートの留保現金を変更すると、中野氏の必要拠出額が自動で再計算される。</t>
+    <t xml:space="preserve">『前提』シートの期首現金（留保する運転資金）を変更すると、中野氏の必要拠出額が自動で再計算される。</t>
   </si>
   <si>
     <r>
@@ -2178,9 +2582,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">株式譲受代金</t>
-  </si>
-  <si>
     <t xml:space="preserve">取得関連費用</t>
   </si>
   <si>
@@ -2282,15 +2683,6 @@
       </rPr>
       <t xml:space="preserve">調達（クロージング時）</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">みずほ銀行 タームローン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">みずほ銀行 ブリッジローン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">榊原氏 出資</t>
   </si>
   <si>
     <r>
@@ -2300,7 +2692,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">中野氏 出資（資本金</t>
+      <t xml:space="preserve">みずほ銀行 タームローン（</t>
     </r>
     <r>
       <rPr>
@@ -2310,7 +2702,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">A</t>
     </r>
     <r>
       <rPr>
@@ -2319,30 +2711,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">万円）＋株主貸付</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">差引（ゼロであること）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">合併後の有利子負債</t>
-  </si>
-  <si>
-    <t xml:space="preserve">合併後の現預金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ネットデット</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ネットデット／</t>
+      <t xml:space="preserve">＋</t>
     </r>
     <r>
       <rPr>
@@ -2352,6 +2721,84 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">みずほ銀行 ブリッジローン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">榊原氏 出資</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中野氏 出資（資本金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円）＋株主貸付</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">差引（ゼロであること）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">合併後の有利子負債</t>
+  </si>
+  <si>
+    <t xml:space="preserve">合併後の現預金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ネットデット</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ネットデット／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">EBITDA</t>
     </r>
   </si>
@@ -2363,27 +2810,37 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">※ ブリッジローンはクロージング後、対象会社の余剰現預金をもって全額返済する。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-※ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">留保する現金を</t>
+      <t xml:space="preserve">※ ブリッジローンはクロージング後、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と対象会社を合併したうえで対象会社の余剰現預金をもって全額返済する。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 留保する現金を</t>
     </r>
     <r>
       <rPr>
@@ -2591,7 +3048,7 @@
     <numFmt numFmtId="168" formatCode="0.00\倍"/>
     <numFmt numFmtId="169" formatCode="0.0\倍"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2733,13 +3190,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="WenQuanYi Zen Hei"/>
@@ -2813,7 +3263,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2870,11 +3320,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2890,11 +3340,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2906,20 +3356,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2979,7 +3425,7 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FFA26769"/>
+      <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
@@ -3020,7 +3466,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>2027年 現金残高の推移（百万円）</a:t>
+              <a:t>2027年 現金残高の推移（百万円）― 保守）</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3043,7 +3489,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>月次CF!A19</c:f>
+              <c:f>'月次CF（保守）'!A21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3093,7 +3539,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>月次CF!$B$5:$M$5</c:f>
+              <c:f>'月次CF（保守）'!$B$5:$M$5</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -3137,45 +3583,45 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>月次CF!$B$19:$M$19</c:f>
+              <c:f>'月次CF（保守）'!$B$21:$M$21</c:f>
               <c:numCache>
                 <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>134.985833333333</c:v>
+                  <c:v>113.319166666667</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>61.9811111111111</c:v>
+                  <c:v>18.6894444444445</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>43.9858333333334</c:v>
+                  <c:v>44.1108333333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>87.9858333333334</c:v>
+                  <c:v>66.5691666666667</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>131.985833333333</c:v>
+                  <c:v>89.0691666666667</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>114.365555555556</c:v>
+                  <c:v>114.615555555556</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>161.370277777778</c:v>
+                  <c:v>140.203611111111</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>101.351388888889</c:v>
+                  <c:v>58.8097222222223</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>81.1013888888889</c:v>
+                  <c:v>81.4763888888889</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>128.106111111111</c:v>
+                  <c:v>107.189444444444</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>172.106111111111</c:v>
+                  <c:v>129.939444444445</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>164.25</c:v>
+                  <c:v>164.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3190,11 +3636,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="96523684"/>
-        <c:axId val="16594243"/>
+        <c:axId val="88100390"/>
+        <c:axId val="17052816"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="96523684"/>
+        <c:axId val="88100390"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3226,7 +3672,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16594243"/>
+        <c:crossAx val="17052816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3234,7 +3680,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16594243"/>
+        <c:axId val="17052816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3250,40 +3696,6 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>現金残高</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
         <c:numFmt formatCode="#,##0;\(#,##0\);\-" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3310,7 +3722,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96523684"/>
+        <c:crossAx val="88100390"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3388,7 +3800,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>2027年 月次の当月収支（百万円）</a:t>
+              <a:t>2027年 現金残高の推移（百万円）― のれん考慮）</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3403,33 +3815,37 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>月次CF!A16</c:f>
+              <c:f>'月次CF（のれん考慮）'!A21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>当月収支</c:v>
+                  <c:v>現金 期末残高</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="a26769"/>
+              <a:srgbClr val="6d2e46"/>
             </a:solidFill>
-            <a:ln w="0">
-              <a:noFill/>
+            <a:ln w="28080">
+              <a:solidFill>
+                <a:srgbClr val="6d2e46"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:dLbls>
             <c:txPr>
               <a:bodyPr wrap="none"/>
@@ -3457,7 +3873,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>月次CF!$B$5:$M$5</c:f>
+              <c:f>'月次CF（のれん考慮）'!$B$5:$M$5</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -3501,57 +3917,64 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>月次CF!$B$16:$M$16</c:f>
+              <c:f>'月次CF（のれん考慮）'!$B$21:$M$21</c:f>
               <c:numCache>
                 <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>34.9858333333333</c:v>
+                  <c:v>113.319166666667</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-73.0047222222222</c:v>
+                  <c:v>18.6894444444445</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-17.9952777777778</c:v>
+                  <c:v>44.1108333333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>44</c:v>
+                  <c:v>66.5691666666667</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>44</c:v>
+                  <c:v>89.0691666666667</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-17.6202777777778</c:v>
+                  <c:v>114.615555555556</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>47.0047222222222</c:v>
+                  <c:v>140.203611111111</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-60.0188888888889</c:v>
+                  <c:v>150.809722222222</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-20.25</c:v>
+                  <c:v>173.476388888889</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>47.0047222222222</c:v>
+                  <c:v>199.189444444445</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>44</c:v>
+                  <c:v>221.939444444445</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-7.85611111111111</c:v>
+                  <c:v>256.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
         </c:ser>
-        <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
-        <c:axId val="81308065"/>
-        <c:axId val="70808373"/>
-      </c:barChart>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="55087990"/>
+        <c:axId val="13793013"/>
+      </c:lineChart>
       <c:catAx>
-        <c:axId val="81308065"/>
+        <c:axId val="55087990"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3583,7 +4006,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70808373"/>
+        <c:crossAx val="13793013"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3591,7 +4014,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="70808373"/>
+        <c:axId val="13793013"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3633,7 +4056,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81308065"/>
+        <c:crossAx val="55087990"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3696,9 +4119,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>87480</xdr:colOff>
+      <xdr:colOff>452160</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>66960</xdr:rowOff>
+      <xdr:rowOff>138960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3707,7 +4130,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="6286680"/>
-        <a:ext cx="7199640" cy="2951640"/>
+        <a:ext cx="7919640" cy="3023640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3717,31 +4140,36 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>163440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>87480</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>66960</xdr:rowOff>
+      <xdr:colOff>452160</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>138960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 2"/>
+        <xdr:cNvPr id="1" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="9715680"/>
-        <a:ext cx="7199640" cy="2951640"/>
+        <a:off x="0" y="6286680"/>
+        <a:ext cx="7919640" cy="3023640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3930,12 +4358,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4154,61 +4582,167 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
+      <c r="B21" s="6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>38</v>
+        <v>600</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="8" t="n">
-        <v>0.03</v>
+        <v>40</v>
+      </c>
+      <c r="B23" s="9" t="n">
+        <f aca="false">B21+B22</f>
+        <v>2000</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>0.03</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="B25" s="9" t="n">
+        <f aca="false">B21/84</f>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>44</v>
+      <c r="D26" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>2315</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="9" t="n">
+        <f aca="false">B29-B30</f>
+        <v>2685</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="9" t="n">
+        <f aca="false">B31/B32</f>
+        <v>537</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="15" t="n">
+        <f aca="false">B6-B33</f>
+        <v>-9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -4227,62 +4761,62 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="2" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="N3" s="17" t="s">
         <v>25</v>
@@ -4291,7 +4825,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -4335,40 +4869,40 @@
         <v>12</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4430,7 +4964,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="B7" s="18" t="n">
         <f aca="false">前提!$B$5*B6/前提!$N$12</f>
@@ -4487,7 +5021,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">-B7*前提!$B$7</f>
@@ -4544,7 +5078,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B9" s="18" t="n">
         <f aca="false">-前提!$B$8</f>
@@ -4601,7 +5135,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B10" s="12" t="n">
         <f aca="false">SUM(B7:B9)</f>
@@ -4656,513 +5190,636 @@
         <v>528</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="L11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="M11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="N11" s="19" t="n">
+        <f aca="false">SUM(B11:M11)</f>
+        <v>-537</v>
+      </c>
+    </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="18" t="n">
+      <c r="A12" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="19" t="n">
+        <f aca="false">B10+B11</f>
+        <v>-9.76416666666666</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <f aca="false">C10+C11</f>
+        <v>-3.75472222222221</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <f aca="false">D10+D11</f>
+        <v>2.25472222222223</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <f aca="false">E10+E11</f>
+        <v>-0.75</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <f aca="false">F10+F11</f>
+        <v>-0.75</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <f aca="false">G10+G11</f>
+        <v>2.25472222222223</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <f aca="false">H10+H11</f>
+        <v>2.25472222222223</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <f aca="false">I10+I11</f>
+        <v>-12.7688888888889</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <f aca="false">J10+J11</f>
+        <v>-0.75</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <f aca="false">K10+K11</f>
+        <v>2.25472222222223</v>
+      </c>
+      <c r="L12" s="19" t="n">
+        <f aca="false">L10+L11</f>
+        <v>-0.75</v>
+      </c>
+      <c r="M12" s="19" t="n">
+        <f aca="false">M10+M11</f>
+        <v>11.2688888888889</v>
+      </c>
+      <c r="N12" s="19" t="n">
+        <f aca="false">SUM(B12:M12)</f>
+        <v>-8.99999999999995</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="18" t="n">
         <f aca="false">B10</f>
         <v>34.9858333333333</v>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C14" s="18" t="n">
         <f aca="false">C10</f>
         <v>40.9952777777778</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D14" s="18" t="n">
         <f aca="false">D10</f>
         <v>47.0047222222222</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E14" s="18" t="n">
         <f aca="false">E10</f>
         <v>44</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F14" s="18" t="n">
         <f aca="false">F10</f>
         <v>44</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G14" s="18" t="n">
         <f aca="false">G10</f>
         <v>47.0047222222222</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H14" s="18" t="n">
         <f aca="false">H10</f>
         <v>47.0047222222222</v>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I14" s="18" t="n">
         <f aca="false">I10</f>
         <v>31.9811111111111</v>
       </c>
-      <c r="J12" s="18" t="n">
+      <c r="J14" s="18" t="n">
         <f aca="false">J10</f>
         <v>44</v>
       </c>
-      <c r="K12" s="18" t="n">
+      <c r="K14" s="18" t="n">
         <f aca="false">K10</f>
         <v>47.0047222222222</v>
       </c>
-      <c r="L12" s="18" t="n">
+      <c r="L14" s="18" t="n">
         <f aca="false">L10</f>
         <v>44</v>
       </c>
-      <c r="M12" s="18" t="n">
+      <c r="M14" s="18" t="n">
         <f aca="false">M10</f>
         <v>56.0188888888889</v>
       </c>
-      <c r="N12" s="18" t="n">
-        <f aca="false">SUM(B12:M12)</f>
+      <c r="N14" s="18" t="n">
+        <f aca="false">SUM(B14:M14)</f>
         <v>528</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="18" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="18" t="n">
         <f aca="false">IF(B4=2,-前提!$B$16,IF(B4=8,-前提!$B$17,0))</f>
         <v>0</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C15" s="18" t="n">
         <f aca="false">IF(C4=2,-前提!$B$16,IF(C4=8,-前提!$B$17,0))</f>
         <v>-114</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D15" s="18" t="n">
         <f aca="false">IF(D4=2,-前提!$B$16,IF(D4=8,-前提!$B$17,0))</f>
         <v>0</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E15" s="18" t="n">
         <f aca="false">IF(E4=2,-前提!$B$16,IF(E4=8,-前提!$B$17,0))</f>
         <v>0</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F15" s="18" t="n">
         <f aca="false">IF(F4=2,-前提!$B$16,IF(F4=8,-前提!$B$17,0))</f>
         <v>0</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G15" s="18" t="n">
         <f aca="false">IF(G4=2,-前提!$B$16,IF(G4=8,-前提!$B$17,0))</f>
         <v>0</v>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="H15" s="18" t="n">
         <f aca="false">IF(H4=2,-前提!$B$16,IF(H4=8,-前提!$B$17,0))</f>
         <v>0</v>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I15" s="18" t="n">
         <f aca="false">IF(I4=2,-前提!$B$16,IF(I4=8,-前提!$B$17,0))</f>
         <v>-92</v>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J15" s="18" t="n">
         <f aca="false">IF(J4=2,-前提!$B$16,IF(J4=8,-前提!$B$17,0))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="18" t="n">
+      <c r="K15" s="18" t="n">
         <f aca="false">IF(K4=2,-前提!$B$16,IF(K4=8,-前提!$B$17,0))</f>
         <v>0</v>
       </c>
-      <c r="L13" s="18" t="n">
+      <c r="L15" s="18" t="n">
         <f aca="false">IF(L4=2,-前提!$B$16,IF(L4=8,-前提!$B$17,0))</f>
         <v>0</v>
       </c>
-      <c r="M13" s="18" t="n">
+      <c r="M15" s="18" t="n">
         <f aca="false">IF(M4=2,-前提!$B$16,IF(M4=8,-前提!$B$17,0))</f>
         <v>0</v>
       </c>
-      <c r="N13" s="18" t="n">
-        <f aca="false">SUM(B13:M13)</f>
-        <v>-206</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="18" t="n">
-        <f aca="false">IF(MOD(B4,3)=0,-前提!$B$22*前提!$B$23/4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="18" t="n">
-        <f aca="false">IF(MOD(C4,3)=0,-B21*前提!$B$23/4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <f aca="false">IF(MOD(D4,3)=0,-C21*前提!$B$23/4,0)</f>
-        <v>-15</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <f aca="false">IF(MOD(E4,3)=0,-D21*前提!$B$23/4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <f aca="false">IF(MOD(F4,3)=0,-E21*前提!$B$23/4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <f aca="false">IF(MOD(G4,3)=0,-F21*前提!$B$23/4,0)</f>
-        <v>-14.625</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <f aca="false">IF(MOD(H4,3)=0,-G21*前提!$B$23/4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <f aca="false">IF(MOD(I4,3)=0,-H21*前提!$B$23/4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <f aca="false">IF(MOD(J4,3)=0,-I21*前提!$B$23/4,0)</f>
-        <v>-14.25</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <f aca="false">IF(MOD(K4,3)=0,-J21*前提!$B$23/4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="18" t="n">
-        <f aca="false">IF(MOD(L4,3)=0,-K21*前提!$B$23/4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="18" t="n">
-        <f aca="false">IF(MOD(M4,3)=0,-L21*前提!$B$23/4,0)</f>
-        <v>-13.875</v>
-      </c>
-      <c r="N14" s="18" t="n">
-        <f aca="false">SUM(B14:M14)</f>
-        <v>-57.75</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B15" s="18" t="n">
-        <f aca="false">IF(MOD(B4,3)=0,-前提!$B$24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="18" t="n">
-        <f aca="false">IF(MOD(C4,3)=0,-前提!$B$24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <f aca="false">IF(MOD(D4,3)=0,-前提!$B$24,0)</f>
-        <v>-50</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <f aca="false">IF(MOD(E4,3)=0,-前提!$B$24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <f aca="false">IF(MOD(F4,3)=0,-前提!$B$24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <f aca="false">IF(MOD(G4,3)=0,-前提!$B$24,0)</f>
-        <v>-50</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <f aca="false">IF(MOD(H4,3)=0,-前提!$B$24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <f aca="false">IF(MOD(I4,3)=0,-前提!$B$24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <f aca="false">IF(MOD(J4,3)=0,-前提!$B$24,0)</f>
-        <v>-50</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <f aca="false">IF(MOD(K4,3)=0,-前提!$B$24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="18" t="n">
-        <f aca="false">IF(MOD(L4,3)=0,-前提!$B$24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="M15" s="18" t="n">
-        <f aca="false">IF(MOD(M4,3)=0,-前提!$B$24,0)</f>
-        <v>-50</v>
-      </c>
       <c r="N15" s="18" t="n">
         <f aca="false">SUM(B15:M15)</f>
-        <v>-200</v>
+        <v>-206</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="12" t="n">
-        <f aca="false">SUM(B12:B15)</f>
-        <v>34.9858333333333</v>
-      </c>
-      <c r="C16" s="12" t="n">
-        <f aca="false">SUM(C12:C15)</f>
-        <v>-73.0047222222222</v>
-      </c>
-      <c r="D16" s="12" t="n">
-        <f aca="false">SUM(D12:D15)</f>
-        <v>-17.9952777777778</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <f aca="false">SUM(E12:E15)</f>
-        <v>44</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <f aca="false">SUM(F12:F15)</f>
-        <v>44</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <f aca="false">SUM(G12:G15)</f>
-        <v>-17.6202777777778</v>
-      </c>
-      <c r="H16" s="12" t="n">
-        <f aca="false">SUM(H12:H15)</f>
-        <v>47.0047222222222</v>
-      </c>
-      <c r="I16" s="12" t="n">
-        <f aca="false">SUM(I12:I15)</f>
-        <v>-60.0188888888889</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <f aca="false">SUM(J12:J15)</f>
-        <v>-20.25</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <f aca="false">SUM(K12:K15)</f>
-        <v>47.0047222222222</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <f aca="false">SUM(L12:L15)</f>
-        <v>44</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <f aca="false">SUM(M12:M15)</f>
-        <v>-7.85611111111111</v>
-      </c>
-      <c r="N16" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="B16" s="18" t="n">
+        <f aca="false">-前提!$B$23*前提!$B$24/12</f>
+        <v>-5</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <f aca="false">-B23*前提!$B$24/12</f>
+        <v>-4.95833333333333</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <f aca="false">-C23*前提!$B$24/12</f>
+        <v>-4.91666666666667</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <f aca="false">-D23*前提!$B$24/12</f>
+        <v>-4.875</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <f aca="false">-E23*前提!$B$24/12</f>
+        <v>-4.83333333333333</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <f aca="false">-F23*前提!$B$24/12</f>
+        <v>-4.79166666666667</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <f aca="false">-G23*前提!$B$24/12</f>
+        <v>-4.75</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <f aca="false">-H23*前提!$B$24/12</f>
+        <v>-4.70833333333333</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <f aca="false">-I23*前提!$B$24/12</f>
+        <v>-4.66666666666667</v>
+      </c>
+      <c r="K16" s="18" t="n">
+        <f aca="false">-J23*前提!$B$24/12</f>
+        <v>-4.625</v>
+      </c>
+      <c r="L16" s="18" t="n">
+        <f aca="false">-K23*前提!$B$24/12</f>
+        <v>-4.58333333333333</v>
+      </c>
+      <c r="M16" s="18" t="n">
+        <f aca="false">-L23*前提!$B$24/12</f>
+        <v>-4.54166666666666</v>
+      </c>
+      <c r="N16" s="18" t="n">
         <f aca="false">SUM(B16:M16)</f>
-        <v>64.25</v>
+        <v>-57.25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="L17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="M17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="N17" s="18" t="n">
+        <f aca="false">SUM(B17:M17)</f>
+        <v>-200</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="18" t="n">
-        <f aca="false">前提!$B$25</f>
+      <c r="A18" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" s="12" t="n">
+        <f aca="false">SUM(B14:B17)</f>
+        <v>13.3191666666667</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <f aca="false">SUM(C14:C17)</f>
+        <v>-94.6297222222222</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <f aca="false">SUM(D14:D17)</f>
+        <v>25.4213888888889</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <f aca="false">SUM(E14:E17)</f>
+        <v>22.4583333333333</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <f aca="false">SUM(F14:F17)</f>
+        <v>22.5</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <f aca="false">SUM(G14:G17)</f>
+        <v>25.5463888888889</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <f aca="false">SUM(H14:H17)</f>
+        <v>25.5880555555556</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <f aca="false">SUM(I14:I17)</f>
+        <v>-81.3938888888889</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <f aca="false">SUM(J14:J17)</f>
+        <v>22.6666666666667</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <f aca="false">SUM(K14:K17)</f>
+        <v>25.7130555555556</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <f aca="false">SUM(L14:L17)</f>
+        <v>22.75</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <f aca="false">SUM(M14:M17)</f>
+        <v>34.8105555555556</v>
+      </c>
+      <c r="N18" s="12" t="n">
+        <f aca="false">SUM(B18:M18)</f>
+        <v>64.7500000000001</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="18" t="n">
+        <f aca="false">前提!$B$26</f>
         <v>100</v>
       </c>
-      <c r="C18" s="18" t="n">
-        <f aca="false">B19</f>
-        <v>134.985833333333</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <f aca="false">C19</f>
-        <v>61.9811111111111</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <f aca="false">D19</f>
-        <v>43.9858333333334</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <f aca="false">E19</f>
-        <v>87.9858333333334</v>
-      </c>
-      <c r="G18" s="18" t="n">
-        <f aca="false">F19</f>
-        <v>131.985833333333</v>
-      </c>
-      <c r="H18" s="18" t="n">
-        <f aca="false">G19</f>
-        <v>114.365555555556</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <f aca="false">H19</f>
-        <v>161.370277777778</v>
-      </c>
-      <c r="J18" s="18" t="n">
-        <f aca="false">I19</f>
-        <v>101.351388888889</v>
-      </c>
-      <c r="K18" s="18" t="n">
-        <f aca="false">J19</f>
-        <v>81.1013888888889</v>
-      </c>
-      <c r="L18" s="18" t="n">
-        <f aca="false">K19</f>
-        <v>128.106111111111</v>
-      </c>
-      <c r="M18" s="18" t="n">
-        <f aca="false">L19</f>
-        <v>172.106111111111</v>
-      </c>
-      <c r="N18" s="18" t="n">
-        <f aca="false">B18</f>
+      <c r="C20" s="18" t="n">
+        <f aca="false">B21</f>
+        <v>113.319166666667</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <f aca="false">C21</f>
+        <v>18.6894444444445</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <f aca="false">D21</f>
+        <v>44.1108333333334</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <f aca="false">E21</f>
+        <v>66.5691666666667</v>
+      </c>
+      <c r="G20" s="18" t="n">
+        <f aca="false">F21</f>
+        <v>89.0691666666667</v>
+      </c>
+      <c r="H20" s="18" t="n">
+        <f aca="false">G21</f>
+        <v>114.615555555556</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <f aca="false">H21</f>
+        <v>140.203611111111</v>
+      </c>
+      <c r="J20" s="18" t="n">
+        <f aca="false">I21</f>
+        <v>58.8097222222223</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <f aca="false">J21</f>
+        <v>81.4763888888889</v>
+      </c>
+      <c r="L20" s="18" t="n">
+        <f aca="false">K21</f>
+        <v>107.189444444444</v>
+      </c>
+      <c r="M20" s="18" t="n">
+        <f aca="false">L21</f>
+        <v>129.939444444445</v>
+      </c>
+      <c r="N20" s="18" t="n">
+        <f aca="false">B20</f>
         <v>100</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B19" s="19" t="n">
-        <f aca="false">B18+B16</f>
-        <v>134.985833333333</v>
-      </c>
-      <c r="C19" s="19" t="n">
-        <f aca="false">C18+C16</f>
-        <v>61.9811111111111</v>
-      </c>
-      <c r="D19" s="19" t="n">
-        <f aca="false">D18+D16</f>
-        <v>43.9858333333334</v>
-      </c>
-      <c r="E19" s="19" t="n">
-        <f aca="false">E18+E16</f>
-        <v>87.9858333333334</v>
-      </c>
-      <c r="F19" s="19" t="n">
-        <f aca="false">F18+F16</f>
-        <v>131.985833333333</v>
-      </c>
-      <c r="G19" s="19" t="n">
-        <f aca="false">G18+G16</f>
-        <v>114.365555555556</v>
-      </c>
-      <c r="H19" s="19" t="n">
-        <f aca="false">H18+H16</f>
-        <v>161.370277777778</v>
-      </c>
-      <c r="I19" s="19" t="n">
-        <f aca="false">I18+I16</f>
-        <v>101.351388888889</v>
-      </c>
-      <c r="J19" s="19" t="n">
-        <f aca="false">J18+J16</f>
-        <v>81.1013888888889</v>
-      </c>
-      <c r="K19" s="19" t="n">
-        <f aca="false">K18+K16</f>
-        <v>128.106111111111</v>
-      </c>
-      <c r="L19" s="19" t="n">
-        <f aca="false">L18+L16</f>
-        <v>172.106111111111</v>
-      </c>
-      <c r="M19" s="19" t="n">
-        <f aca="false">M18+M16</f>
-        <v>164.25</v>
-      </c>
-      <c r="N19" s="19" t="n">
-        <f aca="false">M19</f>
-        <v>164.25</v>
-      </c>
-    </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B21" s="12" t="n">
-        <f aca="false">前提!$B$22+B15</f>
-        <v>2000</v>
-      </c>
-      <c r="C21" s="12" t="n">
-        <f aca="false">B21+C15</f>
-        <v>2000</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <f aca="false">C21+D15</f>
+      <c r="A21" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="20" t="n">
+        <f aca="false">B20+B18</f>
+        <v>113.319166666667</v>
+      </c>
+      <c r="C21" s="20" t="n">
+        <f aca="false">C20+C18</f>
+        <v>18.6894444444445</v>
+      </c>
+      <c r="D21" s="20" t="n">
+        <f aca="false">D20+D18</f>
+        <v>44.1108333333334</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <f aca="false">E20+E18</f>
+        <v>66.5691666666667</v>
+      </c>
+      <c r="F21" s="20" t="n">
+        <f aca="false">F20+F18</f>
+        <v>89.0691666666667</v>
+      </c>
+      <c r="G21" s="20" t="n">
+        <f aca="false">G20+G18</f>
+        <v>114.615555555556</v>
+      </c>
+      <c r="H21" s="20" t="n">
+        <f aca="false">H20+H18</f>
+        <v>140.203611111111</v>
+      </c>
+      <c r="I21" s="20" t="n">
+        <f aca="false">I20+I18</f>
+        <v>58.8097222222223</v>
+      </c>
+      <c r="J21" s="20" t="n">
+        <f aca="false">J20+J18</f>
+        <v>81.4763888888889</v>
+      </c>
+      <c r="K21" s="20" t="n">
+        <f aca="false">K20+K18</f>
+        <v>107.189444444444</v>
+      </c>
+      <c r="L21" s="20" t="n">
+        <f aca="false">L20+L18</f>
+        <v>129.939444444445</v>
+      </c>
+      <c r="M21" s="20" t="n">
+        <f aca="false">M20+M18</f>
+        <v>164.75</v>
+      </c>
+      <c r="N21" s="20" t="n">
+        <f aca="false">M21</f>
+        <v>164.75</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="12" t="n">
+        <f aca="false">前提!$B$23+B17</f>
+        <v>1983.33333333333</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <f aca="false">B23+C17</f>
+        <v>1966.66666666667</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <f aca="false">C23+D17</f>
         <v>1950</v>
       </c>
-      <c r="E21" s="12" t="n">
-        <f aca="false">D21+E15</f>
-        <v>1950</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <f aca="false">E21+F15</f>
-        <v>1950</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <f aca="false">F21+G15</f>
+      <c r="E23" s="12" t="n">
+        <f aca="false">D23+E17</f>
+        <v>1933.33333333333</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <f aca="false">E23+F17</f>
+        <v>1916.66666666667</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <f aca="false">F23+G17</f>
         <v>1900</v>
       </c>
-      <c r="H21" s="12" t="n">
-        <f aca="false">G21+H15</f>
-        <v>1900</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <f aca="false">H21+I15</f>
-        <v>1900</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <f aca="false">I21+J15</f>
+      <c r="H23" s="12" t="n">
+        <f aca="false">G23+H17</f>
+        <v>1883.33333333333</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <f aca="false">H23+I17</f>
+        <v>1866.66666666667</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <f aca="false">I23+J17</f>
         <v>1850</v>
       </c>
-      <c r="K21" s="12" t="n">
-        <f aca="false">J21+K15</f>
-        <v>1850</v>
-      </c>
-      <c r="L21" s="12" t="n">
-        <f aca="false">K21+L15</f>
-        <v>1850</v>
-      </c>
-      <c r="M21" s="12" t="n">
-        <f aca="false">L21+M15</f>
+      <c r="K23" s="12" t="n">
+        <f aca="false">J23+K17</f>
+        <v>1833.33333333333</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <f aca="false">K23+L17</f>
+        <v>1816.66666666667</v>
+      </c>
+      <c r="M23" s="12" t="n">
+        <f aca="false">L23+M17</f>
         <v>1800</v>
       </c>
-      <c r="N21" s="12" t="n">
-        <f aca="false">M21</f>
+      <c r="N23" s="12" t="n">
+        <f aca="false">M23</f>
         <v>1800</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" s="20" t="n">
-        <f aca="false">MIN(B19:M19)</f>
-        <v>43.9858333333334</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" s="21" t="n">
-        <f aca="false">B24/前提!$B$8</f>
-        <v>2.30302369213317</v>
-      </c>
-    </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B25" s="9" t="n">
-        <f aca="false">N12</f>
-        <v>528</v>
+      <c r="A25" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" s="15" t="n">
+        <f aca="false">MIN(B21:M21)</f>
+        <v>18.6894444444445</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <f aca="false">B25/前提!$B$8</f>
+        <v>0.97854763878587</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B26" s="9" t="n">
-        <f aca="false">-N14-N15</f>
-        <v>257.75</v>
+        <v>107</v>
+      </c>
+      <c r="B26" s="18" t="n">
+        <f aca="false">N14</f>
+        <v>528</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B27" s="22" t="n">
-        <f aca="false">(N12+N13)/B26</f>
-        <v>1.24927255092144</v>
+      <c r="A27" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" s="18" t="n">
+        <f aca="false">-N15</f>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" s="18" t="n">
+        <f aca="false">-N16-N17</f>
+        <v>257.25</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>91</v>
+      <c r="A29" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="22" t="n">
+        <f aca="false">(N14+N15)/B28</f>
+        <v>1.25170068027211</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -5182,7 +5839,1085 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:O32"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="2" style="0" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N3" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="M5" s="13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="18" t="n">
+        <f aca="false">前提!B12</f>
+        <v>18</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <f aca="false">前提!C12</f>
+        <v>20</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <f aca="false">前提!D12</f>
+        <v>22</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <f aca="false">前提!E12</f>
+        <v>21</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <f aca="false">前提!F12</f>
+        <v>21</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <f aca="false">前提!G12</f>
+        <v>22</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <f aca="false">前提!H12</f>
+        <v>22</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <f aca="false">前提!I12</f>
+        <v>17</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <f aca="false">前提!J12</f>
+        <v>21</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <f aca="false">前提!K12</f>
+        <v>22</v>
+      </c>
+      <c r="L6" s="18" t="n">
+        <f aca="false">前提!L12</f>
+        <v>21</v>
+      </c>
+      <c r="M6" s="18" t="n">
+        <f aca="false">前提!M12</f>
+        <v>25</v>
+      </c>
+      <c r="N6" s="18" t="n">
+        <f aca="false">SUM(B6:M6)</f>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="18" t="n">
+        <f aca="false">前提!$B$5*B6/前提!$N$12</f>
+        <v>72.5</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <f aca="false">前提!$B$5*C6/前提!$N$12</f>
+        <v>80.5555555555556</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <f aca="false">前提!$B$5*D6/前提!$N$12</f>
+        <v>88.6111111111111</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <f aca="false">前提!$B$5*E6/前提!$N$12</f>
+        <v>84.5833333333333</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <f aca="false">前提!$B$5*F6/前提!$N$12</f>
+        <v>84.5833333333333</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <f aca="false">前提!$B$5*G6/前提!$N$12</f>
+        <v>88.6111111111111</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <f aca="false">前提!$B$5*H6/前提!$N$12</f>
+        <v>88.6111111111111</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <f aca="false">前提!$B$5*I6/前提!$N$12</f>
+        <v>68.4722222222222</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <f aca="false">前提!$B$5*J6/前提!$N$12</f>
+        <v>84.5833333333333</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <f aca="false">前提!$B$5*K6/前提!$N$12</f>
+        <v>88.6111111111111</v>
+      </c>
+      <c r="L7" s="18" t="n">
+        <f aca="false">前提!$B$5*L6/前提!$N$12</f>
+        <v>84.5833333333333</v>
+      </c>
+      <c r="M7" s="18" t="n">
+        <f aca="false">前提!$B$5*M6/前提!$N$12</f>
+        <v>100.694444444444</v>
+      </c>
+      <c r="N7" s="18" t="n">
+        <f aca="false">SUM(B7:M7)</f>
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="18" t="n">
+        <f aca="false">-B7*前提!$B$7</f>
+        <v>-18.415</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <f aca="false">-C7*前提!$B$7</f>
+        <v>-20.4611111111111</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <f aca="false">-D7*前提!$B$7</f>
+        <v>-22.5072222222222</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <f aca="false">-E7*前提!$B$7</f>
+        <v>-21.4841666666667</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <f aca="false">-F7*前提!$B$7</f>
+        <v>-21.4841666666667</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <f aca="false">-G7*前提!$B$7</f>
+        <v>-22.5072222222222</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <f aca="false">-H7*前提!$B$7</f>
+        <v>-22.5072222222222</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <f aca="false">-I7*前提!$B$7</f>
+        <v>-17.3919444444444</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <f aca="false">-J7*前提!$B$7</f>
+        <v>-21.4841666666667</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <f aca="false">-K7*前提!$B$7</f>
+        <v>-22.5072222222222</v>
+      </c>
+      <c r="L8" s="18" t="n">
+        <f aca="false">-L7*前提!$B$7</f>
+        <v>-21.4841666666667</v>
+      </c>
+      <c r="M8" s="18" t="n">
+        <f aca="false">-M7*前提!$B$7</f>
+        <v>-25.5763888888889</v>
+      </c>
+      <c r="N8" s="18" t="n">
+        <f aca="false">SUM(B8:M8)</f>
+        <v>-257.81</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="18" t="n">
+        <f aca="false">-前提!$B$8</f>
+        <v>-19.0991666666667</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <f aca="false">-前提!$B$8</f>
+        <v>-19.0991666666667</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <f aca="false">-前提!$B$8</f>
+        <v>-19.0991666666667</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <f aca="false">-前提!$B$8</f>
+        <v>-19.0991666666667</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <f aca="false">-前提!$B$8</f>
+        <v>-19.0991666666667</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <f aca="false">-前提!$B$8</f>
+        <v>-19.0991666666667</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <f aca="false">-前提!$B$8</f>
+        <v>-19.0991666666667</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <f aca="false">-前提!$B$8</f>
+        <v>-19.0991666666667</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <f aca="false">-前提!$B$8</f>
+        <v>-19.0991666666667</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <f aca="false">-前提!$B$8</f>
+        <v>-19.0991666666667</v>
+      </c>
+      <c r="L9" s="18" t="n">
+        <f aca="false">-前提!$B$8</f>
+        <v>-19.0991666666667</v>
+      </c>
+      <c r="M9" s="18" t="n">
+        <f aca="false">-前提!$B$8</f>
+        <v>-19.0991666666667</v>
+      </c>
+      <c r="N9" s="18" t="n">
+        <f aca="false">SUM(B9:M9)</f>
+        <v>-229.19</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="12" t="n">
+        <f aca="false">SUM(B7:B9)</f>
+        <v>34.9858333333333</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <f aca="false">SUM(C7:C9)</f>
+        <v>40.9952777777778</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <f aca="false">SUM(D7:D9)</f>
+        <v>47.0047222222222</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <f aca="false">SUM(E7:E9)</f>
+        <v>44</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <f aca="false">SUM(F7:F9)</f>
+        <v>44</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <f aca="false">SUM(G7:G9)</f>
+        <v>47.0047222222222</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <f aca="false">SUM(H7:H9)</f>
+        <v>47.0047222222222</v>
+      </c>
+      <c r="I10" s="12" t="n">
+        <f aca="false">SUM(I7:I9)</f>
+        <v>31.9811111111111</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <f aca="false">SUM(J7:J9)</f>
+        <v>44</v>
+      </c>
+      <c r="K10" s="12" t="n">
+        <f aca="false">SUM(K7:K9)</f>
+        <v>47.0047222222222</v>
+      </c>
+      <c r="L10" s="12" t="n">
+        <f aca="false">SUM(L7:L9)</f>
+        <v>44</v>
+      </c>
+      <c r="M10" s="12" t="n">
+        <f aca="false">SUM(M7:M9)</f>
+        <v>56.0188888888889</v>
+      </c>
+      <c r="N10" s="12" t="n">
+        <f aca="false">SUM(B10:M10)</f>
+        <v>528</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="L11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="M11" s="19" t="n">
+        <f aca="false">-前提!$B$33/12</f>
+        <v>-44.75</v>
+      </c>
+      <c r="N11" s="19" t="n">
+        <f aca="false">SUM(B11:M11)</f>
+        <v>-537</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="19" t="n">
+        <f aca="false">B10+B11</f>
+        <v>-9.76416666666666</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <f aca="false">C10+C11</f>
+        <v>-3.75472222222221</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <f aca="false">D10+D11</f>
+        <v>2.25472222222223</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <f aca="false">E10+E11</f>
+        <v>-0.75</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <f aca="false">F10+F11</f>
+        <v>-0.75</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <f aca="false">G10+G11</f>
+        <v>2.25472222222223</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <f aca="false">H10+H11</f>
+        <v>2.25472222222223</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <f aca="false">I10+I11</f>
+        <v>-12.7688888888889</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <f aca="false">J10+J11</f>
+        <v>-0.75</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <f aca="false">K10+K11</f>
+        <v>2.25472222222223</v>
+      </c>
+      <c r="L12" s="19" t="n">
+        <f aca="false">L10+L11</f>
+        <v>-0.75</v>
+      </c>
+      <c r="M12" s="19" t="n">
+        <f aca="false">M10+M11</f>
+        <v>11.2688888888889</v>
+      </c>
+      <c r="N12" s="19" t="n">
+        <f aca="false">SUM(B12:M12)</f>
+        <v>-8.99999999999995</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="18" t="n">
+        <f aca="false">B10</f>
+        <v>34.9858333333333</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <f aca="false">C10</f>
+        <v>40.9952777777778</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <f aca="false">D10</f>
+        <v>47.0047222222222</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <f aca="false">E10</f>
+        <v>44</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <f aca="false">F10</f>
+        <v>44</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <f aca="false">G10</f>
+        <v>47.0047222222222</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <f aca="false">H10</f>
+        <v>47.0047222222222</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <f aca="false">I10</f>
+        <v>31.9811111111111</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <f aca="false">J10</f>
+        <v>44</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <f aca="false">K10</f>
+        <v>47.0047222222222</v>
+      </c>
+      <c r="L14" s="18" t="n">
+        <f aca="false">L10</f>
+        <v>44</v>
+      </c>
+      <c r="M14" s="18" t="n">
+        <f aca="false">M10</f>
+        <v>56.0188888888889</v>
+      </c>
+      <c r="N14" s="18" t="n">
+        <f aca="false">SUM(B14:M14)</f>
+        <v>528</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="18" t="n">
+        <f aca="false">IF(B4=2,-前提!$B$16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <f aca="false">IF(C4=2,-前提!$B$16,0)</f>
+        <v>-114</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <f aca="false">IF(D4=2,-前提!$B$16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <f aca="false">IF(E4=2,-前提!$B$16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <f aca="false">IF(F4=2,-前提!$B$16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <f aca="false">IF(G4=2,-前提!$B$16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <f aca="false">IF(H4=2,-前提!$B$16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <f aca="false">IF(I4=2,-前提!$B$16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <f aca="false">IF(J4=2,-前提!$B$16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <f aca="false">IF(K4=2,-前提!$B$16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="18" t="n">
+        <f aca="false">IF(L4=2,-前提!$B$16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="18" t="n">
+        <f aca="false">IF(M4=2,-前提!$B$16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="18" t="n">
+        <f aca="false">SUM(B15:M15)</f>
+        <v>-114</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="18" t="n">
+        <f aca="false">-前提!$B$23*前提!$B$24/12</f>
+        <v>-5</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <f aca="false">-B23*前提!$B$24/12</f>
+        <v>-4.95833333333333</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <f aca="false">-C23*前提!$B$24/12</f>
+        <v>-4.91666666666667</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <f aca="false">-D23*前提!$B$24/12</f>
+        <v>-4.875</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <f aca="false">-E23*前提!$B$24/12</f>
+        <v>-4.83333333333333</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <f aca="false">-F23*前提!$B$24/12</f>
+        <v>-4.79166666666667</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <f aca="false">-G23*前提!$B$24/12</f>
+        <v>-4.75</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <f aca="false">-H23*前提!$B$24/12</f>
+        <v>-4.70833333333333</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <f aca="false">-I23*前提!$B$24/12</f>
+        <v>-4.66666666666667</v>
+      </c>
+      <c r="K16" s="18" t="n">
+        <f aca="false">-J23*前提!$B$24/12</f>
+        <v>-4.625</v>
+      </c>
+      <c r="L16" s="18" t="n">
+        <f aca="false">-K23*前提!$B$24/12</f>
+        <v>-4.58333333333333</v>
+      </c>
+      <c r="M16" s="18" t="n">
+        <f aca="false">-L23*前提!$B$24/12</f>
+        <v>-4.54166666666666</v>
+      </c>
+      <c r="N16" s="18" t="n">
+        <f aca="false">SUM(B16:M16)</f>
+        <v>-57.25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="L17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="M17" s="18" t="n">
+        <f aca="false">-前提!$B$25</f>
+        <v>-16.6666666666667</v>
+      </c>
+      <c r="N17" s="18" t="n">
+        <f aca="false">SUM(B17:M17)</f>
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" s="12" t="n">
+        <f aca="false">SUM(B14:B17)</f>
+        <v>13.3191666666667</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <f aca="false">SUM(C14:C17)</f>
+        <v>-94.6297222222222</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <f aca="false">SUM(D14:D17)</f>
+        <v>25.4213888888889</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <f aca="false">SUM(E14:E17)</f>
+        <v>22.4583333333333</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <f aca="false">SUM(F14:F17)</f>
+        <v>22.5</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <f aca="false">SUM(G14:G17)</f>
+        <v>25.5463888888889</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <f aca="false">SUM(H14:H17)</f>
+        <v>25.5880555555556</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <f aca="false">SUM(I14:I17)</f>
+        <v>10.6061111111111</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <f aca="false">SUM(J14:J17)</f>
+        <v>22.6666666666667</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <f aca="false">SUM(K14:K17)</f>
+        <v>25.7130555555556</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <f aca="false">SUM(L14:L17)</f>
+        <v>22.75</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <f aca="false">SUM(M14:M17)</f>
+        <v>34.8105555555556</v>
+      </c>
+      <c r="N18" s="12" t="n">
+        <f aca="false">SUM(B18:M18)</f>
+        <v>156.75</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="18" t="n">
+        <f aca="false">前提!$B$26</f>
+        <v>100</v>
+      </c>
+      <c r="C20" s="18" t="n">
+        <f aca="false">B21</f>
+        <v>113.319166666667</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <f aca="false">C21</f>
+        <v>18.6894444444445</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <f aca="false">D21</f>
+        <v>44.1108333333334</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <f aca="false">E21</f>
+        <v>66.5691666666667</v>
+      </c>
+      <c r="G20" s="18" t="n">
+        <f aca="false">F21</f>
+        <v>89.0691666666667</v>
+      </c>
+      <c r="H20" s="18" t="n">
+        <f aca="false">G21</f>
+        <v>114.615555555556</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <f aca="false">H21</f>
+        <v>140.203611111111</v>
+      </c>
+      <c r="J20" s="18" t="n">
+        <f aca="false">I21</f>
+        <v>150.809722222222</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <f aca="false">J21</f>
+        <v>173.476388888889</v>
+      </c>
+      <c r="L20" s="18" t="n">
+        <f aca="false">K21</f>
+        <v>199.189444444445</v>
+      </c>
+      <c r="M20" s="18" t="n">
+        <f aca="false">L21</f>
+        <v>221.939444444445</v>
+      </c>
+      <c r="N20" s="18" t="n">
+        <f aca="false">B20</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="20" t="n">
+        <f aca="false">B20+B18</f>
+        <v>113.319166666667</v>
+      </c>
+      <c r="C21" s="20" t="n">
+        <f aca="false">C20+C18</f>
+        <v>18.6894444444445</v>
+      </c>
+      <c r="D21" s="20" t="n">
+        <f aca="false">D20+D18</f>
+        <v>44.1108333333334</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <f aca="false">E20+E18</f>
+        <v>66.5691666666667</v>
+      </c>
+      <c r="F21" s="20" t="n">
+        <f aca="false">F20+F18</f>
+        <v>89.0691666666667</v>
+      </c>
+      <c r="G21" s="20" t="n">
+        <f aca="false">G20+G18</f>
+        <v>114.615555555556</v>
+      </c>
+      <c r="H21" s="20" t="n">
+        <f aca="false">H20+H18</f>
+        <v>140.203611111111</v>
+      </c>
+      <c r="I21" s="20" t="n">
+        <f aca="false">I20+I18</f>
+        <v>150.809722222222</v>
+      </c>
+      <c r="J21" s="20" t="n">
+        <f aca="false">J20+J18</f>
+        <v>173.476388888889</v>
+      </c>
+      <c r="K21" s="20" t="n">
+        <f aca="false">K20+K18</f>
+        <v>199.189444444445</v>
+      </c>
+      <c r="L21" s="20" t="n">
+        <f aca="false">L20+L18</f>
+        <v>221.939444444445</v>
+      </c>
+      <c r="M21" s="20" t="n">
+        <f aca="false">M20+M18</f>
+        <v>256.75</v>
+      </c>
+      <c r="N21" s="20" t="n">
+        <f aca="false">M21</f>
+        <v>256.75</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="12" t="n">
+        <f aca="false">前提!$B$23+B17</f>
+        <v>1983.33333333333</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <f aca="false">B23+C17</f>
+        <v>1966.66666666667</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <f aca="false">C23+D17</f>
+        <v>1950</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <f aca="false">D23+E17</f>
+        <v>1933.33333333333</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <f aca="false">E23+F17</f>
+        <v>1916.66666666667</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <f aca="false">F23+G17</f>
+        <v>1900</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <f aca="false">G23+H17</f>
+        <v>1883.33333333333</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <f aca="false">H23+I17</f>
+        <v>1866.66666666667</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <f aca="false">I23+J17</f>
+        <v>1850</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <f aca="false">J23+K17</f>
+        <v>1833.33333333333</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <f aca="false">K23+L17</f>
+        <v>1816.66666666667</v>
+      </c>
+      <c r="M23" s="12" t="n">
+        <f aca="false">L23+M17</f>
+        <v>1800</v>
+      </c>
+      <c r="N23" s="12" t="n">
+        <f aca="false">M23</f>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" s="15" t="n">
+        <f aca="false">MIN(B21:M21)</f>
+        <v>18.6894444444445</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <f aca="false">B25/前提!$B$8</f>
+        <v>0.97854763878587</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" s="18" t="n">
+        <f aca="false">N14</f>
+        <v>528</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" s="18" t="n">
+        <f aca="false">-N15</f>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" s="18" t="n">
+        <f aca="false">-N16-N17</f>
+        <v>257.25</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="22" t="n">
+        <f aca="false">(N14+N15)/B28</f>
+        <v>1.60932944606414</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
@@ -5191,32 +6926,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="B5" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <f aca="false">前提!$B$29</f>
         <v>5000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>150</v>
@@ -5233,14 +6969,14 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>1743</v>
@@ -5248,7 +6984,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B11" s="6" t="n">
         <v>500</v>
@@ -5256,16 +6992,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="B12" s="24" t="n">
-        <f aca="false">-前提!$B$25</f>
+        <f aca="false">-前提!$B$26</f>
         <v>-100</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="B13" s="12" t="n">
         <f aca="false">SUM(B10:B12)</f>
@@ -5274,23 +7010,23 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="B16" s="24" t="n">
-        <f aca="false">前提!$B$22</f>
+        <f aca="false">前提!$B$23</f>
         <v>2000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">B13</f>
@@ -5299,7 +7035,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="B18" s="6" t="n">
         <v>1000</v>
@@ -5307,9 +7043,9 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="B19" s="20" t="n">
+        <v>128</v>
+      </c>
+      <c r="B19" s="15" t="n">
         <f aca="false">B7-B16-B17-B18</f>
         <v>7</v>
       </c>
@@ -5325,7 +7061,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="B22" s="12" t="n">
         <f aca="false">B7-B20</f>
@@ -5334,7 +7070,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="B24" s="12" t="n">
         <f aca="false">B16</f>
@@ -5343,16 +7079,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="B25" s="12" t="n">
-        <f aca="false">前提!$B$25</f>
+        <f aca="false">前提!$B$26</f>
         <v>100</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="B26" s="12" t="n">
         <f aca="false">B24-B25</f>
@@ -5361,7 +7097,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="B27" s="25" t="n">
         <f aca="false">B26/529</f>
@@ -5369,13 +7105,18 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="26" t="s">
-        <v>112</v>
+      <c r="A29" s="2" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
-        <v>113</v>
+      <c r="A30" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
